--- a/data/dividends_info_20260723.xlsx
+++ b/data/dividends_info_20260723.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51.25</v>
+        <v>47.94499969482422</v>
       </c>
       <c r="I2" t="n">
-        <v>0.175609756097561</v>
+        <v>0.187715091402359</v>
       </c>
       <c r="J2" t="n">
         <v>235</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.19999694824219</v>
+        <v>64.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.073619682153792</v>
+        <v>1.085271317829457</v>
       </c>
       <c r="J3" t="n">
         <v>214</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>51.2599983215332</v>
+        <v>47.94499969482422</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1755755032129858</v>
+        <v>0.187715091402359</v>
       </c>
       <c r="J6" t="n">
         <v>144</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.065000057220459</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="I7" t="n">
-        <v>3.728813455997861</v>
+        <v>3.774509874503002</v>
       </c>
       <c r="J7" t="n">
         <v>123</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.89999961853027</v>
+        <v>22.96500015258789</v>
       </c>
       <c r="I8" t="n">
-        <v>1.179039320950559</v>
+        <v>1.175702147642155</v>
       </c>
       <c r="J8" t="n">
         <v>123</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.119999885559082</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="I9" t="n">
-        <v>3.267973917318617</v>
+        <v>3.338898291187508</v>
       </c>
       <c r="J9" t="n">
         <v>116</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.449999809265137</v>
+        <v>7.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8053691481358354</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>88</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.909999847412109</v>
+        <v>4.940000057220459</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7739307776155733</v>
+        <v>0.7692307603207009</v>
       </c>
       <c r="J13" t="n">
         <v>67</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.89999961853027</v>
+        <v>22.96500015258789</v>
       </c>
       <c r="I14" t="n">
-        <v>1.179039320950559</v>
+        <v>1.175702147642155</v>
       </c>
       <c r="J14" t="n">
         <v>60</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>51.2599983215332</v>
+        <v>47.94499969482422</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1755755032129858</v>
+        <v>0.187715091402359</v>
       </c>
       <c r="J15" t="n">
         <v>60</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>91.34999847412109</v>
+        <v>91.25</v>
       </c>
       <c r="I16" t="n">
-        <v>1.455938721637506</v>
+        <v>1.457534246575342</v>
       </c>
       <c r="J16" t="n">
         <v>60</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.519999980926514</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="I17" t="n">
-        <v>5.434782627474683</v>
+        <v>5.319149062089187</v>
       </c>
       <c r="J17" t="n">
         <v>53</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.940000057220459</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="I19" t="n">
-        <v>7.482993051639355</v>
+        <v>8.593750192085285</v>
       </c>
       <c r="J19" t="n">
         <v>18</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.909999847412109</v>
+        <v>4.940000057220459</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7739307776155733</v>
+        <v>0.7692307603207009</v>
       </c>
       <c r="J20" t="n">
         <v>11</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.849999904632568</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="I21" t="n">
-        <v>5.191894910574625</v>
+        <v>5.173741448512964</v>
       </c>
       <c r="J21" t="n">
         <v>11</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.96999979019165</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I22" t="n">
-        <v>4.187604837285504</v>
+        <v>4.222972918549448</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.179999828338623</v>
+        <v>4.090000152587891</v>
       </c>
       <c r="I23" t="n">
-        <v>3.349282434196755</v>
+        <v>3.422982757382465</v>
       </c>
       <c r="J23" t="n">
         <v>-3</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9.968000411987305</v>
+        <v>9.817999839782715</v>
       </c>
       <c r="I24" t="n">
-        <v>2.608346601664759</v>
+        <v>2.648197232052044</v>
       </c>
       <c r="J24" t="n">
         <v>-3</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13.52000045776367</v>
+        <v>13.5600004196167</v>
       </c>
       <c r="I25" t="n">
-        <v>4.437869672226663</v>
+        <v>4.424778624136357</v>
       </c>
       <c r="J25" t="n">
         <v>-3</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.599999904632568</v>
+        <v>2.563999891281128</v>
       </c>
       <c r="I26" t="n">
-        <v>8.461538771905854</v>
+        <v>8.58034357755276</v>
       </c>
       <c r="J26" t="n">
         <v>-3</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6.545000076293945</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="I28" t="n">
-        <v>3.666921271235463</v>
+        <v>3.703703692802077</v>
       </c>
       <c r="J28" t="n">
         <v>-3</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5.699999809265137</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="I31" t="n">
-        <v>2.105263228341595</v>
+        <v>2.101576168096538</v>
       </c>
       <c r="J31" t="n">
         <v>-10</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>8.699999809265137</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5747126562779011</v>
+        <v>0.5617977768886342</v>
       </c>
       <c r="J32" t="n">
         <v>-10</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.839999914169312</v>
+        <v>2.759999990463257</v>
       </c>
       <c r="I33" t="n">
-        <v>5.281690300468702</v>
+        <v>5.434782627474683</v>
       </c>
       <c r="J33" t="n">
         <v>-10</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.140000104904175</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I34" t="n">
-        <v>3.971962422114281</v>
+        <v>4.009434178699683</v>
       </c>
       <c r="J34" t="n">
         <v>-17</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4.320000171661377</v>
+        <v>4.449999809265137</v>
       </c>
       <c r="I35" t="n">
-        <v>1.620370305982639</v>
+        <v>1.573033775288176</v>
       </c>
       <c r="J35" t="n">
         <v>-17</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>33.65000152587891</v>
+        <v>32.09999847412109</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4457652100985518</v>
+        <v>0.4672897418388648</v>
       </c>
       <c r="J36" t="n">
         <v>-17</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9.649999618530273</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="I37" t="n">
-        <v>23.13886101831865</v>
+        <v>23.25937407575551</v>
       </c>
       <c r="J37" t="n">
         <v>-17</v>
@@ -4029,7 +4029,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4090,14 +4090,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4114,7 +4114,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4124,14 +4124,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4148,7 +4148,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4175,14 +4175,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4192,14 +4192,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4216,7 +4216,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4226,14 +4226,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4250,7 +4250,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4260,14 +4260,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4277,14 +4277,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4294,14 +4294,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4318,7 +4318,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4328,14 +4328,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4369,7 +4369,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4379,14 +4379,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4396,14 +4396,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4430,14 +4430,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4464,14 +4464,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4488,7 +4488,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4505,7 +4505,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4515,14 +4515,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4532,14 +4532,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4549,14 +4549,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4566,14 +4566,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4583,14 +4583,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4600,14 +4600,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4641,7 +4641,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4668,14 +4668,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4692,7 +4692,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4702,14 +4702,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4719,14 +4719,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4736,14 +4736,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4753,14 +4753,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4777,7 +4777,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4794,7 +4794,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4828,7 +4828,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4838,14 +4838,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4855,14 +4855,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4913,7 +4913,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4923,14 +4923,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4940,14 +4940,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4957,14 +4957,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4974,14 +4974,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4991,14 +4991,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5015,7 +5015,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5025,14 +5025,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5066,7 +5066,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5083,7 +5083,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5100,7 +5100,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5127,14 +5127,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5144,14 +5144,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5219,7 +5219,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5236,7 +5236,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5253,7 +5253,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5280,14 +5280,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5297,14 +5297,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5314,14 +5314,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5331,14 +5331,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5365,14 +5365,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5382,14 +5382,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5406,7 +5406,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5423,7 +5423,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5457,7 +5457,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5467,14 +5467,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5491,7 +5491,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5518,14 +5518,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5535,14 +5535,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5552,14 +5552,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5586,14 +5586,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5603,14 +5603,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5627,7 +5627,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5644,7 +5644,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5654,14 +5654,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5678,7 +5678,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5688,14 +5688,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5705,14 +5705,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5722,14 +5722,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5746,7 +5746,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5756,14 +5756,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5780,7 +5780,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5797,7 +5797,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5814,7 +5814,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5920,78 +5920,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>OPS Retail S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RAI WAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>The Italian Sea Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>